--- a/artfynd/A 60367-2024 artfynd.xlsx
+++ b/artfynd/A 60367-2024 artfynd.xlsx
@@ -675,40 +675,39 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114567667</v>
+        <v>114567672</v>
       </c>
       <c r="B2" t="n">
-        <v>104737</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
@@ -719,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578578</v>
+        <v>578191</v>
       </c>
       <c r="R2" t="n">
-        <v>6673891</v>
+        <v>6674025</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,12 +784,7 @@
         <v>114568380</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114568383</v>
+        <v>114568382</v>
       </c>
       <c r="B4" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +930,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>578179</v>
+        <v>578163</v>
       </c>
       <c r="R4" t="n">
-        <v>6674065</v>
+        <v>6674055</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114567672</v>
+        <v>114568383</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,7 +1023,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr"/>
@@ -1052,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>578191</v>
+        <v>578179</v>
       </c>
       <c r="R5" t="n">
-        <v>6674025</v>
+        <v>6674065</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,22 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Alexandra Holmgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114567443</v>
+        <v>114567667</v>
       </c>
       <c r="B6" t="n">
-        <v>96616</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106244</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1131,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1159,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>578139</v>
+        <v>578578</v>
       </c>
       <c r="R6" t="n">
-        <v>6673985</v>
+        <v>6673891</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,51 +1194,42 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Louise Almén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114568382</v>
+        <v>114567443</v>
       </c>
       <c r="B7" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1270,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>578163</v>
+        <v>578139</v>
       </c>
       <c r="R7" t="n">
-        <v>6674055</v>
+        <v>6673985</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1296,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alexandra Holmgren</t>
+          <t>Louise Almén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 60367-2024 artfynd.xlsx
+++ b/artfynd/A 60367-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567672</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114568380</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114568382</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114568383</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567667</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1300,8 +1330,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114567443</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>